--- a/system_analysis_v.xlsx
+++ b/system_analysis_v.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Structures in the System" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,31 +31,31 @@
     <t>Unique bond count</t>
   </si>
   <si>
+    <t>CoIn2</t>
+  </si>
+  <si>
     <t>CoIn3</t>
   </si>
   <si>
-    <t>CoIn2</t>
+    <t>Mg2Cu</t>
+  </si>
+  <si>
+    <t>U3Si2</t>
   </si>
   <si>
     <t>IrIn3</t>
   </si>
   <si>
-    <t>U3Si2</t>
-  </si>
-  <si>
     <t>RuIn3</t>
   </si>
   <si>
-    <t>Mg2Cu</t>
-  </si>
-  <si>
     <t>Co-Co</t>
   </si>
   <si>
+    <t>In-In</t>
+  </si>
+  <si>
     <t>Co-In</t>
-  </si>
-  <si>
-    <t>In-In</t>
   </si>
 </sst>
 </file>
@@ -461,10 +461,10 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -478,15 +478,15 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -512,15 +512,15 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -529,15 +529,15 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -563,15 +563,15 @@
         <v>12</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -580,10 +580,10 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -614,10 +614,10 @@
         <v>12</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -631,10 +631,10 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
